--- a/output/supplementary/P1_chi2_pathway_reporting.xlsx
+++ b/output/supplementary/P1_chi2_pathway_reporting.xlsx
@@ -445,10 +445,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.216</v>
+        <v>0.698</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5289</v>
+        <v>0.7053</v>
       </c>
       <c r="D2" t="b">
         <v>0</v>
@@ -461,10 +461,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.054</v>
+        <v>0.42</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7881</v>
+        <v>0.8107</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
@@ -477,10 +477,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.627</v>
+        <v>1.173</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6534</v>
+        <v>0.5562</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
@@ -493,10 +493,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.033</v>
+        <v>0.026</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7932</v>
+        <v>0.9873</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
@@ -509,10 +509,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.744</v>
+        <v>0.899</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6272</v>
+        <v>0.638</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
@@ -525,10 +525,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.832</v>
+        <v>2.826</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2802</v>
+        <v>0.2435</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.741</v>
+        <v>3.629</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1917</v>
+        <v>0.1629</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.555</v>
+        <v>24.281</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
